--- a/artfynd/A 58087-2025 artfynd.xlsx
+++ b/artfynd/A 58087-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>107140201</v>
+        <v>107140152</v>
       </c>
       <c r="B2" t="n">
-        <v>88896</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>720</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593674.6902324784</v>
+        <v>593675</v>
       </c>
       <c r="R2" t="n">
-        <v>6786734.160367188</v>
+        <v>6786735</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -791,37 +786,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>107140220</v>
+        <v>107140201</v>
       </c>
       <c r="B3" t="n">
-        <v>88937</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91375</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>256756</v>
+        <v>720</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blek fingersvamp</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramaria pallida</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Ricken</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593674.6902324784</v>
+        <v>593675</v>
       </c>
       <c r="R3" t="n">
-        <v>6786734.160367188</v>
+        <v>6786735</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -907,37 +897,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>107140139</v>
+        <v>107140191</v>
       </c>
       <c r="B4" t="n">
-        <v>90174</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2014</v>
+        <v>788</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Pers.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593674.6902324784</v>
+        <v>593675</v>
       </c>
       <c r="R4" t="n">
-        <v>6786734.160367188</v>
+        <v>6786735</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1023,40 +1008,39 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>107140152</v>
+        <v>113426200</v>
       </c>
       <c r="B5" t="n">
-        <v>90138</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93196</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>366</v>
+        <v>1435</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1066,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593674.6902324784</v>
+        <v>593675</v>
       </c>
       <c r="R5" t="n">
-        <v>6786734.160367188</v>
+        <v>6786735</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,37 +1123,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>107140115</v>
+        <v>107140139</v>
       </c>
       <c r="B6" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92732</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>2014</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1182,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593674.6902324784</v>
+        <v>593675</v>
       </c>
       <c r="R6" t="n">
-        <v>6786734.160367188</v>
+        <v>6786735</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1255,37 +1234,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>107176029</v>
+        <v>107140115</v>
       </c>
       <c r="B7" t="n">
-        <v>88921</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5741</v>
+        <v>5964</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1298,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593674.6902324784</v>
+        <v>593675</v>
       </c>
       <c r="R7" t="n">
-        <v>6786734.160367188</v>
+        <v>6786735</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,7 +1302,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2015-09-19</t>
+          <t>2014-08-30</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1338,7 +1312,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2015-09-19</t>
+          <t>2014-08-30</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1371,15 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>107140191</v>
+        <v>116376512</v>
       </c>
       <c r="B8" t="n">
-        <v>91607</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,25 +1356,33 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>788</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1444,22 +1421,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2014-08-30</t>
+          <t>2015-11-05</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2014-08-30</t>
+          <t>2015-11-05</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,42 +1464,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113426200</v>
+        <v>113425851</v>
       </c>
       <c r="B9" t="n">
-        <v>91604</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1435</v>
+        <v>4363</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -1530,17 +1502,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kolarkojan, Hamnäs, Skog, Hls</t>
+          <t>Skogsbilväg, Hamnäs, Skog, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593675</v>
+        <v>594024</v>
       </c>
       <c r="R9" t="n">
-        <v>6786735</v>
+        <v>6786671</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1564,22 +1536,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2014-08-30</t>
+          <t>2016-07-03</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2014-08-30</t>
+          <t>2016-07-03</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,15 +1579,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>116376512</v>
+        <v>129835513</v>
       </c>
       <c r="B10" t="n">
-        <v>91729</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>61491</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1623,48 +1590,62 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>106670</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Arion ater ater</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kolarkojan, Hamnäs, Skog, Hls</t>
+          <t>Skogsbilväg, Hamnäs, Skog, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593675</v>
+        <v>594024</v>
       </c>
       <c r="R10" t="n">
-        <v>6786735</v>
+        <v>6786671</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1688,7 +1669,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2015-11-05</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1698,12 +1679,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2015-11-05</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,6 +1709,775 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>118422156</v>
+      </c>
+      <c r="B11" t="n">
+        <v>43378</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>201075</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Brunfläckig pärlemorfjäril</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Boloria selene</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skogsbilväg, Hamnäs, Skog, Hls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>594024</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6786671</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Skog</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jan Lundstedt</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jan Lundstedt</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>104316669</v>
+      </c>
+      <c r="B12" t="n">
+        <v>43464</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>201116</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Berggräsfjäril</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lasiommata petropolitana</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skogsbilväg, Hamnäs, Skog, Hls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>594024</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6786671</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Skog</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-06-21</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-06-21</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jan Lundstedt</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jan Lundstedt</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>104185412</v>
+      </c>
+      <c r="B13" t="n">
+        <v>43309</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>201146</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Silverblåvinge</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Polyommatus amandus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Schneider, 1792)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skogsbilväg, Hamnäs, Skog, Hls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>594024</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6786671</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Skog</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2017-06-29</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2017-06-29</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jan Lundstedt</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jan Lundstedt</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122278487</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skogsbilväg, Hamnäs, Skog, Hls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>594024</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6786671</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skog</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-08-26</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-08-26</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jan Lundstedt</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jan Lundstedt</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>113803522</v>
+      </c>
+      <c r="B15" t="n">
+        <v>56876</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>208257</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kopparödla</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Anguis fragilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skogsbilväg, Hamnäs, Skog, Hls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>594024</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6786671</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Skog</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jan Lundstedt</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jan Lundstedt</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129841884</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99163</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>264981</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Skogsnattviol × grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora × chlorantha</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Skogsbilväg, Hamnäs, Skog, Hls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>594024</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6786671</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Skog</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jan Lundstedt</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jan Lundstedt</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58087-2025 artfynd.xlsx
+++ b/artfynd/A 58087-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107140152</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107140201</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107140191</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113426200</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1231,6 +1256,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107140139</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1346,6 +1376,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113425851</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1457,6 +1492,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107140115</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1576,6 +1616,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116376512</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1709,6 +1754,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129835513</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1842,6 +1892,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118422156</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1967,6 +2022,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104316669</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2092,6 +2152,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104185412</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2225,6 +2290,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122278487</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2354,6 +2424,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113803522</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2478,8 +2553,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129841884</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>